--- a/wildlife/reports/United-Kingdom/composition/Oxford/Birds/composition.xlsx
+++ b/wildlife/reports/United-Kingdom/composition/Oxford/Birds/composition.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Woodpigeon</t>
+          <t>Canada Goose</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -473,7 +473,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Herring Gull</t>
+          <t>Woodpigeon</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -483,37 +483,37 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Canada Goose</t>
+          <t>Street Pigeon</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Street Pigeon</t>
+          <t>Herring Gull</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Greylag Goose</t>
+          <t>Magpie</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Magpie</t>
+          <t>Greylag Goose</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -523,17 +523,17 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Red Kite</t>
+          <t>Black-Headed Gull</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Mute Swan</t>
+          <t>Grey Heron</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -543,7 +543,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Black-Headed Gull</t>
+          <t>Mute Swan</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -553,7 +553,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Grey Heron</t>
+          <t>Red Kite</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -573,7 +573,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Blackbird</t>
+          <t>Robin</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -583,7 +583,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Robin</t>
+          <t>Blackbird</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -593,7 +593,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Moorhen</t>
+          <t>Chiffchaff</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -603,7 +603,7 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Chiffchaff</t>
+          <t>Moorhen</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -613,7 +613,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>House Sparrow</t>
+          <t>Green Woodpecker</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -623,7 +623,7 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Lesser Black-Backed Gull</t>
+          <t>Cormorant</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -633,7 +633,7 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Green Woodpecker</t>
+          <t>Pied Wagtail</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -643,7 +643,7 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Great Tit</t>
+          <t>Lesser Black-Backed Gull</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -653,7 +653,7 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Pied Wagtail</t>
+          <t>House Sparrow</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -663,7 +663,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Cormorant</t>
+          <t>Rook</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -673,7 +673,7 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Rook</t>
+          <t>Coot</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -683,7 +683,7 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Coot</t>
+          <t>Great Tit</t>
         </is>
       </c>
       <c r="B26" t="n">

--- a/wildlife/reports/United-Kingdom/composition/Oxford/Birds/composition.xlsx
+++ b/wildlife/reports/United-Kingdom/composition/Oxford/Birds/composition.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -467,23 +467,23 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Woodpigeon</t>
+          <t>Street Pigeon</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Street Pigeon</t>
+          <t>Woodpigeon</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">

--- a/wildlife/reports/United-Kingdom/composition/Oxford/Birds/composition.xlsx
+++ b/wildlife/reports/United-Kingdom/composition/Oxford/Birds/composition.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -457,63 +457,63 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Canada Goose</t>
+          <t>Woodpigeon</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Street Pigeon</t>
+          <t>Herring Gull</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Woodpigeon</t>
+          <t>Canada Goose</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Herring Gull</t>
+          <t>Street Pigeon</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Magpie</t>
+          <t>Greylag Goose</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Greylag Goose</t>
+          <t>Magpie</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -523,17 +523,17 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Black-Headed Gull</t>
+          <t>Red Kite</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Grey Heron</t>
+          <t>Mute Swan</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -543,7 +543,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Mute Swan</t>
+          <t>Black-Headed Gull</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -553,7 +553,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Red Kite</t>
+          <t>Grey Heron</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -573,7 +573,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Robin</t>
+          <t>Blackbird</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -583,7 +583,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Blackbird</t>
+          <t>Robin</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -593,7 +593,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Chiffchaff</t>
+          <t>Moorhen</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -603,7 +603,7 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Moorhen</t>
+          <t>Chiffchaff</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -613,7 +613,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Green Woodpecker</t>
+          <t>House Sparrow</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -623,7 +623,7 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Cormorant</t>
+          <t>Lesser Black-Backed Gull</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -633,7 +633,7 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Pied Wagtail</t>
+          <t>Green Woodpecker</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -643,7 +643,7 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Lesser Black-Backed Gull</t>
+          <t>Great Tit</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -653,7 +653,7 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>House Sparrow</t>
+          <t>Pied Wagtail</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -663,7 +663,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Rook</t>
+          <t>Cormorant</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -673,7 +673,7 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Coot</t>
+          <t>Rook</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -683,7 +683,7 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Great Tit</t>
+          <t>Coot</t>
         </is>
       </c>
       <c r="B26" t="n">

--- a/wildlife/reports/United-Kingdom/composition/Oxford/Birds/composition.xlsx
+++ b/wildlife/reports/United-Kingdom/composition/Oxford/Birds/composition.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -457,63 +457,63 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Woodpigeon</t>
+          <t>Canada Goose</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Herring Gull</t>
+          <t>Street Pigeon</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Canada Goose</t>
+          <t>Woodpigeon</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Street Pigeon</t>
+          <t>Herring Gull</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Greylag Goose</t>
+          <t>Magpie</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Magpie</t>
+          <t>Greylag Goose</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -523,17 +523,17 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Red Kite</t>
+          <t>Black-Headed Gull</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Mute Swan</t>
+          <t>Grey Heron</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -543,7 +543,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Black-Headed Gull</t>
+          <t>Mute Swan</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -553,7 +553,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Grey Heron</t>
+          <t>Red Kite</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -573,7 +573,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Blackbird</t>
+          <t>Robin</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -583,7 +583,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Robin</t>
+          <t>Blackbird</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -593,7 +593,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Moorhen</t>
+          <t>Chiffchaff</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -603,7 +603,7 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Chiffchaff</t>
+          <t>Moorhen</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -613,7 +613,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>House Sparrow</t>
+          <t>Green Woodpecker</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -623,7 +623,7 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Lesser Black-Backed Gull</t>
+          <t>Cormorant</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -633,7 +633,7 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Green Woodpecker</t>
+          <t>Pied Wagtail</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -643,7 +643,7 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Great Tit</t>
+          <t>Lesser Black-Backed Gull</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -653,7 +653,7 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Pied Wagtail</t>
+          <t>House Sparrow</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -663,7 +663,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Cormorant</t>
+          <t>Rook</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -673,7 +673,7 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Rook</t>
+          <t>Coot</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -683,7 +683,7 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Coot</t>
+          <t>Great Tit</t>
         </is>
       </c>
       <c r="B26" t="n">
